--- a/attendance_excel/CS/FY/Python_Programming.xlsx
+++ b/attendance_excel/CS/FY/Python_Programming.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,10 +434,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -459,10 +474,10 @@
           <t>P</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -484,10 +499,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -509,10 +524,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -534,10 +549,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -559,12 +574,147 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
